--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -1,58 +1,495 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <bookViews>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
+  <si>
+    <t>ClassId</t>
+  </si>
+  <si>
+    <t>ClassName</t>
+  </si>
+  <si>
+    <t>PrimaryStat</t>
+  </si>
+  <si>
+    <t>CombatConvertCoeffs</t>
+  </si>
+  <si>
+    <t>AttackRange</t>
+  </si>
+  <si>
+    <t>MeleeWindupSeconds</t>
+  </si>
+  <si>
+    <t>RangedProjectileSpeed</t>
+  </si>
+  <si>
+    <t>RangedTimeoutSeconds</t>
+  </si>
+  <si>
+    <t>Class_Warrior</t>
+  </si>
+  <si>
+    <t>战士</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
+  </si>
+  <si>
+    <t>Class_Archer</t>
+  </si>
+  <si>
+    <t>射手</t>
+  </si>
+  <si>
+    <t>Agility</t>
+  </si>
+  <si>
+    <t>Class_Mage</t>
+  </si>
+  <si>
+    <t>法师</t>
+  </si>
+  <si>
+    <t>Intelligence</t>
+  </si>
+  <si>
+    <t>Class_Knight</t>
+  </si>
+  <si>
+    <t>骑士</t>
+  </si>
+  <si>
+    <t>Class_Rogue</t>
+  </si>
+  <si>
+    <t>盗贼</t>
+  </si>
+  <si>
+    <t>Class_Priest</t>
+  </si>
+  <si>
+    <t>牧师</t>
+  </si>
+  <si>
+    <t>Class_Berserker</t>
+  </si>
+  <si>
+    <t>狂战士</t>
+  </si>
+  <si>
+    <t>Class_Ranger</t>
+  </si>
+  <si>
+    <t>游侠</t>
+  </si>
+  <si>
+    <t>Class_Warlock</t>
+  </si>
+  <si>
+    <t>术士</t>
+  </si>
+  <si>
+    <t>Class_Paladin</t>
+  </si>
+  <si>
+    <t>圣骑士</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="21">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -60,18 +497,312 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -391,58 +1122,62 @@
       </a:style>
     </a:lnDef>
   </a:objectDefaults>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:H11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <cols>
+    <col min="4" max="4" width="113.75" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>ClassId</v>
-      </c>
-      <c r="B1" t="str">
-        <v>ClassName</v>
-      </c>
-      <c r="C1" t="str">
-        <v>PrimaryStat</v>
-      </c>
-      <c r="D1" t="str">
-        <v>CombatConvertCoeffs</v>
-      </c>
-      <c r="E1" t="str">
-        <v>AttackRange</v>
-      </c>
-      <c r="F1" t="str">
-        <v>MeleeWindupSeconds</v>
-      </c>
-      <c r="G1" t="str">
-        <v>RangedProjectileSpeed</v>
-      </c>
-      <c r="H1" t="str">
-        <v>RangedTimeoutSeconds</v>
+    <row r="1" spans="1:8">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>Class_Warrior</v>
-      </c>
-      <c r="B2" t="str">
-        <v>战士</v>
-      </c>
-      <c r="C2" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="D2" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
+    <row r="2" spans="1:8">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="F2">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -451,76 +1186,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Class_Archer</v>
-      </c>
-      <c r="B3" t="str">
-        <v>射手</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Agility</v>
-      </c>
-      <c r="D3" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>5.2</v>
+        <v>2.5</v>
       </c>
       <c r="F3">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G3">
         <v>13</v>
       </c>
       <c r="H3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4">
         <v>2</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>Class_Mage</v>
-      </c>
-      <c r="B4" t="str">
-        <v>法师</v>
-      </c>
-      <c r="C4" t="str">
-        <v>Intelligence</v>
-      </c>
-      <c r="D4" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
-      </c>
-      <c r="E4">
-        <v>5.4</v>
-      </c>
       <c r="F4">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G4">
         <v>14</v>
       </c>
       <c r="H4">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>Class_Knight</v>
-      </c>
-      <c r="B5" t="str">
-        <v>骑士</v>
-      </c>
-      <c r="C5" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="D5" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
       <c r="E5">
-        <v>1.9500000000000002</v>
+        <v>0.8</v>
       </c>
       <c r="F5">
-        <v>0.38</v>
+        <v>0.5</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -529,24 +1264,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>Class_Rogue</v>
-      </c>
-      <c r="B6" t="str">
-        <v>盗贼</v>
-      </c>
-      <c r="C6" t="str">
-        <v>Agility</v>
-      </c>
-      <c r="D6" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>11</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="F6">
-        <v>0.38999999999999996</v>
+        <v>0.5</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -555,24 +1290,24 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>Class_Priest</v>
-      </c>
-      <c r="B7" t="str">
-        <v>牧师</v>
-      </c>
-      <c r="C7" t="str">
-        <v>Intelligence</v>
-      </c>
-      <c r="D7" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
       </c>
       <c r="E7">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G7">
         <v>17</v>
@@ -581,24 +1316,24 @@
         <v>2</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>Class_Berserker</v>
-      </c>
-      <c r="B8" t="str">
-        <v>狂战士</v>
-      </c>
-      <c r="C8" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="D8" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
       </c>
       <c r="E8">
-        <v>2.1</v>
+        <v>0.5</v>
       </c>
       <c r="F8">
-        <v>0.41</v>
+        <v>0.5</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -607,76 +1342,76 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>Class_Ranger</v>
-      </c>
-      <c r="B9" t="str">
-        <v>游侠</v>
-      </c>
-      <c r="C9" t="str">
-        <v>Agility</v>
-      </c>
-      <c r="D9" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" t="s">
+        <v>11</v>
       </c>
       <c r="E9">
-        <v>6.4</v>
+        <v>2</v>
       </c>
       <c r="F9">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G9">
         <v>19</v>
       </c>
       <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B10" t="s">
+        <v>29</v>
+      </c>
+      <c r="C10" t="s">
+        <v>17</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10">
         <v>2</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>Class_Warlock</v>
-      </c>
-      <c r="B10" t="str">
-        <v>术士</v>
-      </c>
-      <c r="C10" t="str">
-        <v>Intelligence</v>
-      </c>
-      <c r="D10" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
-      </c>
-      <c r="E10">
-        <v>6.6</v>
-      </c>
       <c r="F10">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="G10">
         <v>20</v>
       </c>
       <c r="H10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>Class_Paladin</v>
-      </c>
-      <c r="B11" t="str">
-        <v>圣骑士</v>
-      </c>
-      <c r="C11" t="str">
-        <v>Strength</v>
-      </c>
-      <c r="D11" t="str">
-        <v>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</v>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s">
+        <v>11</v>
       </c>
       <c r="E11">
-        <v>2.25</v>
+        <v>0.8</v>
       </c>
       <c r="F11">
-        <v>0.43999999999999995</v>
+        <v>0.5</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -686,8 +1421,10 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H11"/>
+    <ignoredError sqref="A1:H1 A2:D11 G2:H2 G3:G4 G5:H8 G9:G10 G11:H11" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
@@ -27,7 +32,55 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="57">
+  <si>
+    <t>职业ID</t>
+  </si>
+  <si>
+    <t>职业名</t>
+  </si>
+  <si>
+    <t>主属性</t>
+  </si>
+  <si>
+    <t>战斗换算系数</t>
+  </si>
+  <si>
+    <t>攻击距离</t>
+  </si>
+  <si>
+    <t>近战前摇</t>
+  </si>
+  <si>
+    <t>远程弹速</t>
+  </si>
+  <si>
+    <t>远程超时</t>
+  </si>
+  <si>
+    <t>主键；被 SoulConfig.ClassId 引用</t>
+  </si>
+  <si>
+    <t>参与 WarriorName；外观 ClassAffinity 精确匹配键</t>
+  </si>
+  <si>
+    <t>Strength | Agility | Intelligence</t>
+  </si>
+  <si>
+    <t>键_数值|…；缺键回退全局默认</t>
+  </si>
+  <si>
+    <t>进入攻击态距离</t>
+  </si>
+  <si>
+    <t>≥0 秒；Melee 时用</t>
+  </si>
+  <si>
+    <t>≥0；Ranged 时用</t>
+  </si>
+  <si>
+    <t>≥0 秒</t>
+  </si>
   <si>
     <t>ClassId</t>
   </si>
@@ -65,6 +118,12 @@
     <t>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
   </si>
   <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
     <t>Class_Archer</t>
   </si>
   <si>
@@ -74,6 +133,12 @@
     <t>Agility</t>
   </si>
   <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
     <t>Class_Mage</t>
   </si>
   <si>
@@ -83,6 +148,9 @@
     <t>Intelligence</t>
   </si>
   <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>Class_Knight</t>
   </si>
   <si>
@@ -101,6 +169,12 @@
     <t>牧师</t>
   </si>
   <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>Class_Berserker</t>
   </si>
   <si>
@@ -113,10 +187,16 @@
     <t>游侠</t>
   </si>
   <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>Class_Warlock</t>
   </si>
   <si>
     <t>术士</t>
+  </si>
+  <si>
+    <t>20</t>
   </si>
   <si>
     <t>Class_Paladin</t>
@@ -135,14 +215,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,153 +671,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -797,7 +870,7 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -881,7 +954,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -916,7 +988,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -951,16 +1022,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -1082,56 +1157,17 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
-    <col min="4" max="4" width="113.75" customWidth="1"/>
+    <col min="4" max="4" width="10.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1173,258 +1209,307 @@
       <c r="D2" t="s">
         <v>11</v>
       </c>
-      <c r="E2">
-        <v>0.5</v>
-      </c>
-      <c r="F2">
-        <v>0.5</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="H2">
-        <v>0</v>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3">
-        <v>2.5</v>
-      </c>
-      <c r="F3">
-        <v>0.5</v>
-      </c>
-      <c r="G3">
-        <v>13</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E4">
-        <v>2</v>
-      </c>
-      <c r="F4">
-        <v>0.5</v>
-      </c>
-      <c r="G4">
-        <v>14</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
+        <v>0.3</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E5">
-        <v>0.8</v>
-      </c>
-      <c r="F5">
-        <v>0.5</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E6">
-        <v>0.5</v>
-      </c>
-      <c r="F6">
-        <v>0.5</v>
-      </c>
-      <c r="G6">
-        <v>0</v>
-      </c>
-      <c r="H6">
-        <v>0</v>
+        <v>0.8</v>
+      </c>
+      <c r="F6" t="s">
+        <v>28</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="C7" t="s">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="F7">
-        <v>0.5</v>
-      </c>
-      <c r="G7">
-        <v>17</v>
-      </c>
-      <c r="H7">
-        <v>2</v>
+        <v>0.3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>28</v>
+      </c>
+      <c r="G7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="C8" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E8">
-        <v>0.5</v>
-      </c>
-      <c r="F8">
-        <v>0.5</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="F8" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" t="s">
+        <v>29</v>
+      </c>
+      <c r="H8" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" t="s">
         <v>27</v>
       </c>
-      <c r="C9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
       <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9">
-        <v>0.5</v>
-      </c>
-      <c r="G9">
-        <v>19</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
+        <v>1.2</v>
+      </c>
+      <c r="F9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" t="s">
+        <v>26</v>
+      </c>
+      <c r="D10" t="s">
+        <v>27</v>
+      </c>
+      <c r="E10">
+        <v>0.3</v>
+      </c>
+      <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="B10" t="s">
+      <c r="G10" t="s">
         <v>29</v>
       </c>
-      <c r="C10" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10">
-        <v>0.5</v>
-      </c>
-      <c r="G10">
-        <v>20</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
+      <c r="H10" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E11">
-        <v>0.8</v>
-      </c>
-      <c r="F11">
+        <v>1.1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G11" t="s">
+        <v>51</v>
+      </c>
+      <c r="H11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <v>0.9</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>54</v>
+      </c>
+      <c r="H12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>55</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13">
         <v>0.5</v>
       </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
-  <ignoredErrors>
-    <ignoredError sqref="A1:H1 A2:D11 G2:H2 G3:G4 G5:H8 G9:G10 G11:H11" numberStoredAsText="1"/>
-  </ignoredErrors>
 </worksheet>
 </file>
--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -368,12 +368,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -692,7 +698,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -716,16 +722,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -734,90 +740,91 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1167,7 +1174,9 @@
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
+    <col min="3" max="3" width="17.125" customWidth="1"/>
     <col min="4" max="4" width="10.125" customWidth="1"/>
+    <col min="5" max="5" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1222,29 +1231,29 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
-      <c r="A3" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:8">
+      <c r="A3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="H3" t="s">
+      <c r="H3" s="1" t="s">
         <v>23</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -1,37 +1,49 @@
 
-<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
+<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
+  <HeadingPairs>
+    <vt:vector size="2" baseType="variant">
+      <vt:variant>
+        <vt:lpstr>工作表</vt:lpstr>
+      </vt:variant>
+      <vt:variant>
+        <vt:i4>1</vt:i4>
+      </vt:variant>
+    </vt:vector>
+  </HeadingPairs>
+  <TitlesOfParts>
+    <vt:vector size="1" baseType="lpstr">
+      <vt:lpstr>Sheet1</vt:lpstr>
+    </vt:vector>
+  </TitlesOfParts>
+</Properties>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
+<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
+  <dc:creator>openpyxl</dc:creator>
+  <cp:lastModifiedBy>王玉栋</cp:lastModifiedBy>
+  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-06T09:58:00Z</dcterms:created>
+  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-07T02:04:45Z</dcterms:modified>
+</cp:coreProperties>
+</file>
+
+<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
+<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
+    <vt:lpwstr>83B2D260CABF4B8EB01364A4BE897255_12</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
+    <vt:lpwstr>2052-12.1.0.28043</vt:lpwstr>
+  </property>
+  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="CalculationRule">
+    <vt:i4>0</vt:i4>
+  </property>
+</Properties>
+</file>
+
+<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="57">
   <si>
     <t>职业ID</t>
@@ -115,7 +127,7 @@
     <t>Strength</t>
   </si>
   <si>
-    <t>NormalAttackPrimaryMult_1.5|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
+    <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
   </si>
   <si>
     <t>0.5</t>
@@ -207,7 +219,7 @@
 </sst>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -886,7 +898,7 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1168,7 +1180,39 @@
 </a:theme>
 </file>
 
-<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
+</file>
+
+<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H13"/>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -1,50 +1,38 @@
 
-<file path=docProps\app.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <Application>Microsoft Excel Compatible / Openpyxl 3.1.5</Application>
-  <HeadingPairs>
-    <vt:vector size="2" baseType="variant">
-      <vt:variant>
-        <vt:lpstr>工作表</vt:lpstr>
-      </vt:variant>
-      <vt:variant>
-        <vt:i4>1</vt:i4>
-      </vt:variant>
-    </vt:vector>
-  </HeadingPairs>
-  <TitlesOfParts>
-    <vt:vector size="1" baseType="lpstr">
-      <vt:lpstr>Sheet1</vt:lpstr>
-    </vt:vector>
-  </TitlesOfParts>
-</Properties>
+<file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <bookViews>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
+  </bookViews>
+  <sheets>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+  </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
+</workbook>
 </file>
 
-<file path=docProps\core.xml><?xml version="1.0" encoding="utf-8"?>
-<cp:coreProperties xmlns:cp="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:dcmitype="http://purl.org/dc/dcmitype/" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance">
-  <dc:creator>openpyxl</dc:creator>
-  <cp:lastModifiedBy>王玉栋</cp:lastModifiedBy>
-  <dcterms:created xsi:type="dcterms:W3CDTF">2026-08-06T09:58:00Z</dcterms:created>
-  <dcterms:modified xsi:type="dcterms:W3CDTF">2026-08-07T02:04:45Z</dcterms:modified>
-</cp:coreProperties>
-</file>
-
-<file path=docProps\custom.xml><?xml version="1.0" encoding="utf-8"?>
-<Properties xmlns="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="2" name="ICV">
-    <vt:lpwstr>83B2D260CABF4B8EB01364A4BE897255_12</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="3" name="KSOProductBuildVer">
-    <vt:lpwstr>2052-12.1.0.28043</vt:lpwstr>
-  </property>
-  <property fmtid="{D5CDD505-2E9C-101B-9397-08002B2CF9AE}" pid="4" name="CalculationRule">
-    <vt:i4>0</vt:i4>
-  </property>
-</Properties>
-</file>
-
-<file path=xl\sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="57">
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
   <si>
     <t>职业ID</t>
   </si>
@@ -70,6 +58,9 @@
     <t>远程超时</t>
   </si>
   <si>
+    <t>追击移动速度系数</t>
+  </si>
+  <si>
     <t>主键；被 SoulConfig.ClassId 引用</t>
   </si>
   <si>
@@ -94,6 +85,9 @@
     <t>≥0 秒</t>
   </si>
   <si>
+    <t>≥0；仅 GoalKind=AttackSlot 时×移速；缺省1</t>
+  </si>
+  <si>
     <t>ClassId</t>
   </si>
   <si>
@@ -116,6 +110,9 @@
   </si>
   <si>
     <t>RangedTimeoutSeconds</t>
+  </si>
+  <si>
+    <t>ChaseMoveSpeedMult</t>
   </si>
   <si>
     <t>Class_Warrior</t>
@@ -219,7 +216,7 @@
 </sst>
 </file>
 
-<file path=xl\styles.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
@@ -689,148 +686,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -898,7 +895,7 @@
 </styleSheet>
 </file>
 
-<file path=xl\theme\theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
@@ -1180,50 +1177,18 @@
 </a:theme>
 </file>
 
-<file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Work\Cursor\Gravedigger2026\Gravedigger2026\Gravedigger2026\Assets\ConfigTables\Excel\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
-  </bookViews>
-  <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-  </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
-</workbook>
-</file>
-
-<file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="17.125" customWidth="1"/>
     <col min="4" max="4" width="10.125" customWidth="1"/>
     <col min="5" max="5" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1248,317 +1213,356 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" spans="1:8">
+    <row r="3" s="1" customFormat="1" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="I3" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4">
         <v>0.3</v>
       </c>
       <c r="F4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H4" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="I4">
+        <v>1.5</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:9">
       <c r="A5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B5" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" t="s">
         <v>30</v>
-      </c>
-      <c r="B5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" t="s">
-        <v>27</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>0.8</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E7">
         <v>0.3</v>
       </c>
       <c r="F7" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H7" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E8">
         <v>0.3</v>
       </c>
       <c r="F8" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H8" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E9">
         <v>1.2</v>
       </c>
       <c r="F9" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="H9" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>0.3</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H10" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E11">
         <v>1.1</v>
       </c>
       <c r="F11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="I11">
+        <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C12" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E12">
         <v>0.9</v>
       </c>
       <c r="F12" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
-        <v>34</v>
+        <v>37</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C13" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E13">
         <v>0.5</v>
       </c>
       <c r="F13" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G13" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H13" t="s">
-        <v>29</v>
+        <v>32</v>
+      </c>
+      <c r="I13">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="62">
   <si>
     <t>职业ID</t>
   </si>
@@ -212,6 +212,12 @@
   </si>
   <si>
     <t>圣骑士</t>
+  </si>
+  <si>
+    <t>Class_Servants</t>
+  </si>
+  <si>
+    <t>仆从</t>
   </si>
 </sst>
 </file>
@@ -1180,7 +1186,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="17.125" customWidth="1"/>
@@ -1301,7 +1307,7 @@
         <v>32</v>
       </c>
       <c r="I4">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -1330,7 +1336,7 @@
         <v>37</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -1359,7 +1365,7 @@
         <v>37</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1388,7 +1394,7 @@
         <v>32</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -1417,7 +1423,7 @@
         <v>32</v>
       </c>
       <c r="I8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -1446,7 +1452,7 @@
         <v>49</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -1475,7 +1481,7 @@
         <v>32</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -1562,7 +1568,36 @@
         <v>32</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" t="s">
+        <v>30</v>
+      </c>
+      <c r="E14">
+        <v>0.3</v>
+      </c>
+      <c r="F14" t="s">
+        <v>31</v>
+      </c>
+      <c r="G14" t="s">
+        <v>32</v>
+      </c>
+      <c r="H14" t="s">
+        <v>32</v>
+      </c>
+      <c r="I14">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="17.125" customWidth="1" min="3" max="3"/>
@@ -1064,45 +1064,50 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>转职职业</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>等级</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>主属性</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>战斗换算系数</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>攻击距离</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>近战前摇</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>远程弹速</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>远程超时</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>追击移动速度系数</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>制造默认获得技能ID</t>
         </is>
@@ -1121,50 +1126,55 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CSV 中文：战士|射手|法师|盗贼 → 枚举；空/非法→Unspecified；预留后续魔法书等条件；不参与命名/外观/PrimaryStat/战斗；不烘进实例</t>
+          <t>CSV 中文：战士|射手|法师|刺客 → 枚举；空/非法→Unspecified；预留后续魔法书等条件；不参与命名/外观/PrimaryStat/战斗；不烘进实例</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>可选文字；空=无转职目标；本轮仅填表，不驱动玩法</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>≥0；仅 UI 展示（UI-016 士兵卡职业名下 Lv.{ClassLevel}）；不参与战斗/制造公式；缺/空 → 0</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Strength | Agility | Intelligence</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>键_数值|…；缺键回退全局默认</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>进入攻击态距离</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>≥0 秒；Melee 时用</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>≥0；Ranged 时用</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>≥0 秒</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>≥0；仅 GoalKind=AttackSlot 时×移速；缺省1</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>空=无；SkillId 或 SkillId|SkillId；FK → SkillConfig.SkillId</t>
         </is>
@@ -1188,45 +1198,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>PromoteClass</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>ClassLevel</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="F3" s="1" t="inlineStr">
         <is>
           <t>PrimaryStat</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="G3" s="1" t="inlineStr">
         <is>
           <t>CombatConvertCoeffs</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="H3" s="1" t="inlineStr">
         <is>
           <t>AttackRange</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="I3" s="1" t="inlineStr">
         <is>
           <t>MeleeWindupSeconds</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="J3" s="1" t="inlineStr">
         <is>
           <t>RangedProjectileSpeed</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="K3" s="1" t="inlineStr">
         <is>
           <t>RangedTimeoutSeconds</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>ChaseMoveSpeedMult</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>DefaultSkillIds</t>
         </is>
@@ -1248,41 +1263,41 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>0.3</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>2</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Skill_01</t>
         </is>
@@ -1304,38 +1319,38 @@
           <t>射手</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Agility</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>1</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1355,38 +1370,38 @@
           <t>法师</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>0.8</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1406,38 +1421,38 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>0.3</v>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1449,46 +1464,46 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>盗贼</t>
+          <t>刺客</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>盗贼</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
         <v>1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>Agility</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>0.3</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1508,38 +1523,38 @@
           <t>法师</t>
         </is>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>1</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1.2</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1559,38 +1574,38 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>1</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>0.3</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1610,38 +1625,38 @@
           <t>射手</t>
         </is>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>Agility</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1.1</v>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1661,38 +1676,38 @@
           <t>法师</t>
         </is>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>Intelligence</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>0.9</v>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="K12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1712,38 +1727,38 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>0.5</v>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" t="n">
+      <c r="L13" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1763,38 +1778,38 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>Strength</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>0.3</v>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>0.5</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>2.5</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -1038,7 +1038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M14"/>
+  <dimension ref="A1:N14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col width="17.125" customWidth="1" min="3" max="3"/>
@@ -1104,10 +1104,15 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>基础移速</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>追击移动速度系数</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>制造默认获得技能ID</t>
         </is>
@@ -1171,10 +1176,15 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
+          <t>&gt;=0；世界单位/秒；士兵 MoveSpeed 维 Base；缺/&lt;=0 -&gt; 3.5</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
           <t>≥0；仅 GoalKind=AttackSlot 时×移速；缺省1</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>空=无；SkillId 或 SkillId|SkillId；FK → SkillConfig.SkillId</t>
         </is>
@@ -1238,10 +1248,15 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
+          <t>BaseMoveSpeed</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
           <t>ChaseMoveSpeedMult</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>DefaultSkillIds</t>
         </is>
@@ -1295,9 +1310,12 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M4" t="n">
         <v>2</v>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Skill_01</t>
         </is>
@@ -1351,6 +1369,9 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M5" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1402,6 +1423,9 @@
         </is>
       </c>
       <c r="L6" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M6" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1453,6 +1477,9 @@
         </is>
       </c>
       <c r="L7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M7" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1504,6 +1531,9 @@
         </is>
       </c>
       <c r="L8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M8" t="n">
         <v>3</v>
       </c>
     </row>
@@ -1555,6 +1585,9 @@
         </is>
       </c>
       <c r="L9" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M9" t="n">
         <v>0.5</v>
       </c>
     </row>
@@ -1606,6 +1639,9 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M10" t="n">
         <v>2</v>
       </c>
     </row>
@@ -1657,6 +1693,9 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M11" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1708,6 +1747,9 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M12" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1759,6 +1801,9 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M13" t="n">
         <v>1.5</v>
       </c>
     </row>
@@ -1810,6 +1855,9 @@
         </is>
       </c>
       <c r="L14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M14" t="n">
         <v>2.5</v>
       </c>
     </row>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -2,374 +2,39 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12255" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="1">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -377,306 +42,15 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1029,6 +403,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1039,12 +414,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:N14"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5"/>
-  <cols>
-    <col width="17.125" customWidth="1" min="3" max="3"/>
-    <col width="10.125" customWidth="1" min="4" max="4"/>
-    <col width="8.875" customWidth="1" min="5" max="5"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1059,17 +429,17 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>基础职业</t>
+          <t>BaseClass</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>转职职业</t>
+          <t>PromoteClass</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>等级</t>
+          <t>ClassLevel</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -1104,17 +474,17 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>基础移速</t>
+          <t>BaseMoveSpeed</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>追击移动速度系数</t>
+          <t>ChaseMoveSpeedMult</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>制造默认获得技能ID</t>
+          <t>DefaultSkillIds</t>
         </is>
       </c>
     </row>
@@ -1131,17 +501,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CSV 中文：战士|射手|法师|刺客 → 枚举；空/非法→Unspecified；预留后续魔法书等条件；不参与命名/外观/PrimaryStat/战斗；不烘进实例</t>
+          <t>（待补 SPEC 中文说明）BaseClass</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>可选文字；空=无转职目标；本轮仅填表，不驱动玩法</t>
+          <t>（待补 SPEC 中文说明）PromoteClass</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>≥0；仅 UI 展示（UI-016 士兵卡职业名下 Lv.{ClassLevel}）；不参与战斗/制造公式；缺/空 → 0</t>
+          <t>（待补 SPEC 中文说明）ClassLevel</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -1176,27 +546,27 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>&gt;=0；世界单位/秒；士兵 MoveSpeed 维 Base；缺/&lt;=0 -&gt; 3.5</t>
+          <t>（待补 SPEC 中文说明）BaseMoveSpeed</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>≥0；仅 GoalKind=AttackSlot 时×移速；缺省1</t>
+          <t>（待补 SPEC 中文说明）ChaseMoveSpeedMult</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>空=无；SkillId 或 SkillId|SkillId；FK → SkillConfig.SkillId</t>
+          <t>（待补 SPEC 中文说明）DefaultSkillIds</t>
         </is>
       </c>
     </row>
-    <row r="3" customFormat="1" s="1">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="3">
+      <c r="A3" t="inlineStr">
         <is>
           <t>ClassId</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>ClassName</t>
         </is>
@@ -1216,32 +586,32 @@
           <t>ClassLevel</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>PrimaryStat</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>CombatConvertCoeffs</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>AttackRange</t>
         </is>
       </c>
-      <c r="I3" s="1" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>MeleeWindupSeconds</t>
         </is>
       </c>
-      <c r="J3" s="1" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>RangedProjectileSpeed</t>
         </is>
       </c>
-      <c r="K3" s="1" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>RangedTimeoutSeconds</t>
         </is>
@@ -1278,8 +648,11 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="E4" t="n">
-        <v>1</v>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1291,8 +664,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>0.3</v>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -1309,11 +684,15 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>2</v>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1337,8 +716,11 @@
           <t>射手</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>1</v>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1350,8 +732,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>1</v>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -1368,12 +752,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1391,8 +780,11 @@
           <t>法师</t>
         </is>
       </c>
-      <c r="E6" t="n">
-        <v>1</v>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1404,8 +796,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H6" t="n">
-        <v>0.8</v>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.8</t>
+        </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -1422,12 +816,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L6" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1445,8 +844,11 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>1</v>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1458,8 +860,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H7" t="n">
-        <v>0.3</v>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1476,12 +880,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M7" t="n">
-        <v>2</v>
-      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1499,8 +908,11 @@
           <t>刺客</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>1</v>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1512,8 +924,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H8" t="n">
-        <v>0.3</v>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1530,12 +944,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3</v>
-      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1553,8 +972,11 @@
           <t>法师</t>
         </is>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1566,8 +988,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H9" t="n">
-        <v>1.2</v>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.2</t>
+        </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1584,12 +1008,17 @@
           <t>2</t>
         </is>
       </c>
-      <c r="L9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.5</v>
-      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1607,8 +1036,11 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1620,8 +1052,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H10" t="n">
-        <v>0.3</v>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1638,12 +1072,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M10" t="n">
-        <v>2</v>
-      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1661,8 +1100,11 @@
           <t>射手</t>
         </is>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1674,8 +1116,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H11" t="n">
-        <v>1.1</v>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.1</t>
+        </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1692,12 +1136,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1</v>
-      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1715,8 +1164,11 @@
           <t>法师</t>
         </is>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1728,8 +1180,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H12" t="n">
-        <v>0.9</v>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1746,12 +1200,17 @@
           <t>1</t>
         </is>
       </c>
-      <c r="L12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1</v>
-      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1769,8 +1228,11 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1782,8 +1244,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H13" t="n">
-        <v>0.5</v>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1800,12 +1264,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M13" t="n">
-        <v>1.5</v>
-      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1823,8 +1292,11 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1836,8 +1308,10 @@
           <t>NormalAttackPrimaryMult_15|AttackSpeedBase_0.5|AttackSpeedAgiDiv_60|SkillCdIntDiv_30|SkillCdFloor_0.1</t>
         </is>
       </c>
-      <c r="H14" t="n">
-        <v>0.3</v>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1854,12 +1328,17 @@
           <t>0</t>
         </is>
       </c>
-      <c r="L14" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="M14" t="n">
-        <v>2.5</v>
-      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/制造_职业配置表_Manufacture_ClassConfig.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,11 @@
           <t>DefaultSkillIds</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>士兵简画图标</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -559,6 +564,11 @@
           <t>（待补 SPEC 中文说明）DefaultSkillIds</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>UI-033 战斗指示器简画；仅文件名；Resources/UI/Icons/{Id}；空=空框</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -631,6 +641,11 @@
           <t>DefaultSkillIds</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>SilhouetteIconAssetId</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -648,7 +663,6 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>1</t>
@@ -699,6 +713,7 @@
           <t>Skill_01</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -716,7 +731,6 @@
           <t>射手</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>1</t>
@@ -762,7 +776,7 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -780,7 +794,6 @@
           <t>法师</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>1</t>
@@ -826,7 +839,7 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -844,7 +857,6 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>1</t>
@@ -890,7 +902,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -908,7 +920,6 @@
           <t>刺客</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>1</t>
@@ -954,7 +965,7 @@
           <t>3</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -972,7 +983,6 @@
           <t>法师</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>1</t>
@@ -1018,7 +1028,7 @@
           <t>0.5</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1036,7 +1046,6 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>1</t>
@@ -1082,7 +1091,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1100,7 +1109,6 @@
           <t>射手</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>1</t>
@@ -1146,7 +1154,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1164,7 +1172,6 @@
           <t>法师</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>1</t>
@@ -1210,7 +1217,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1228,7 +1235,6 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>1</t>
@@ -1274,7 +1280,7 @@
           <t>1.5</t>
         </is>
       </c>
-      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1292,7 +1298,6 @@
           <t>战士</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>1</t>
@@ -1338,7 +1343,7 @@
           <t>2.5</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
